--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,157 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E8" s="3">
         <v>23700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -864,8 +870,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -923,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +958,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E12" s="3">
         <v>28600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>25700</v>
       </c>
       <c r="G12" s="3">
         <v>25700</v>
       </c>
       <c r="H12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I12" s="3">
         <v>20000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8600</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1080,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,8 +1097,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1087,21 +1106,21 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-1600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1114,8 +1133,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1123,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E17" s="3">
         <v>38300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-32800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-31100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-26500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-10400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,126 +1375,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1700</v>
       </c>
       <c r="J20" s="3">
         <v>1700</v>
       </c>
       <c r="K20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-28900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-27500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-10800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1484,8 +1523,8 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1511,8 +1550,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1520,72 +1559,78 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>200</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1593,24 +1638,24 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1618,28 +1663,31 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3">
         <v>-9800</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3">
         <v>-9800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2117,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1700</v>
       </c>
       <c r="J32" s="3">
         <v>-1700</v>
       </c>
       <c r="K32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3">
         <v>-9800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3">
         <v>-9800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,47 +2482,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E41" s="3">
         <v>104100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>66200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>58300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>112100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>147600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>240400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>435300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>129500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>145900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,38 +2542,41 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>277700</v>
+      </c>
+      <c r="E42" s="3">
         <v>234400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>193000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>175800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>189300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>211300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>227800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>206100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>135400</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2500,8 +2589,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2515,47 +2604,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E43" s="3">
         <v>5100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,8 +2666,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2633,47 +2728,50 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E45" s="3">
         <v>7100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,47 +2790,50 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>338800</v>
+      </c>
+      <c r="E46" s="3">
         <v>350700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>268500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>239500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>260200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>306900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>352900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>368000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>391200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>449000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>143000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>155900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,37 +2852,40 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E47" s="3">
         <v>66000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>41100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>70100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>77100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>57000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>33900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45300</v>
-      </c>
-      <c r="L47" s="3">
-        <v>7600</v>
       </c>
       <c r="M47" s="3">
         <v>7600</v>
@@ -2789,8 +2893,8 @@
       <c r="N47" s="3">
         <v>7600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>7600</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2810,47 +2914,50 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E48" s="3">
         <v>39300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2869,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2928,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,8 +3162,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3055,38 +3174,38 @@
         <v>1600</v>
       </c>
       <c r="E52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F52" s="3">
         <v>1400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1500</v>
       </c>
       <c r="G52" s="3">
         <v>1500</v>
       </c>
       <c r="H52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="I52" s="3">
         <v>1300</v>
       </c>
       <c r="J52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,47 +3286,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>432200</v>
+      </c>
+      <c r="E54" s="3">
         <v>457500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>349600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>347500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>373800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>398800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>421400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>446000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>442400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>462000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>158400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>168000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,47 +3398,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3328,8 +3458,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3364,11 +3497,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3387,47 +3520,50 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E59" s="3">
         <v>22200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,47 +3582,50 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E60" s="3">
         <v>24600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,8 +3644,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3541,11 +3683,11 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3564,47 +3706,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E62" s="3">
         <v>34700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>45800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>42100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>44800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>45900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>44600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>47500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>30400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,47 +3954,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E66" s="3">
         <v>59300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>73500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4033,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>150200</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -4059,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,47 +4288,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-299300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-264800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-254800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-225300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-197200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-170200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-143600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-116900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-97800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-79300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-58300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-44000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,47 +4536,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>368400</v>
+      </c>
+      <c r="E76" s="3">
         <v>398300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>269500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>278300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>300900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>324100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>347900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>371800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>387800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>404400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-47700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-35700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4413,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3">
         <v>-9800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,31 +4815,32 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>500</v>
       </c>
       <c r="I83" s="3">
+        <v>500</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -4651,7 +4849,7 @@
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -4668,8 +4866,8 @@
       <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>200</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4677,8 +4875,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-25000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,44 +5273,45 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-700</v>
       </c>
       <c r="K91" s="3">
         <v>-700</v>
       </c>
       <c r="L91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -5099,22 +5319,25 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-68500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>20700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-72100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-174000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>7000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,58 +5791,61 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>135100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>17600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>322700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>109700</v>
-      </c>
-      <c r="O100" s="3">
-        <v>100</v>
       </c>
       <c r="P100" s="3">
         <v>100</v>
       </c>
       <c r="Q100" s="3">
+        <v>100</v>
+      </c>
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -5608,8 +5853,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5667,63 +5915,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-52900</v>
+      </c>
+      <c r="E102" s="3">
         <v>37900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-35500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-92800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-194900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>305800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>130000</v>
-      </c>
-      <c r="O102" s="3">
-        <v>-8600</v>
       </c>
       <c r="P102" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="Q102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,163 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +880,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E12" s="3">
         <v>31300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>28600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>25700</v>
       </c>
       <c r="H12" s="3">
         <v>25700</v>
       </c>
       <c r="I12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="J12" s="3">
         <v>20000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8600</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1100,8 +1120,8 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1109,21 +1129,21 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1136,8 +1156,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1145,8 +1165,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E17" s="3">
         <v>41000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-32800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-31100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-10400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,132 +1409,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E20" s="3">
         <v>3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1700</v>
       </c>
       <c r="K20" s="3">
         <v>1700</v>
       </c>
       <c r="L20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-33600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-27500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-20700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-10800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1526,8 +1566,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1553,8 +1593,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1562,103 +1602,109 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1666,28 +1712,31 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7900</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3">
         <v>-9800</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3">
         <v>-9800</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1700</v>
       </c>
       <c r="K32" s="3">
         <v>-1700</v>
       </c>
       <c r="L32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3">
         <v>-9800</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3">
         <v>-9800</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E41" s="3">
         <v>51200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>104100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>66200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>58300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>147600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>240400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>435300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>129500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>145900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,41 +2632,44 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>244600</v>
+      </c>
+      <c r="E42" s="3">
         <v>277700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>234400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>193000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>175800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>189300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>211300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>227800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>206100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>135400</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2592,8 +2682,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2607,50 +2697,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2731,50 +2827,53 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E45" s="3">
         <v>6200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,50 +2892,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>304500</v>
+      </c>
+      <c r="E46" s="3">
         <v>338800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>350700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>268500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>239500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>260200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>306900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>352900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>368000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>391200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>449000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>143000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>155900</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,40 +2957,43 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E47" s="3">
         <v>51300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>41100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>70100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>77100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>57000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>33900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45300</v>
-      </c>
-      <c r="M47" s="3">
-        <v>7600</v>
       </c>
       <c r="N47" s="3">
         <v>7600</v>
@@ -2896,8 +3001,8 @@
       <c r="O47" s="3">
         <v>7600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>7600</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2917,50 +3022,53 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E48" s="3">
         <v>40500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,8 +3087,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,50 +3282,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E52" s="3">
         <v>1600</v>
       </c>
       <c r="F52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G52" s="3">
         <v>1400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1500</v>
       </c>
       <c r="H52" s="3">
         <v>1500</v>
       </c>
       <c r="I52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="J52" s="3">
         <v>1300</v>
       </c>
       <c r="K52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>406800</v>
+      </c>
+      <c r="E54" s="3">
         <v>432200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>457500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>349600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>347500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>373800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>398800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>421400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>446000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>442400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>462000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>158400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>168000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,50 +3529,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,8 +3592,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3500,11 +3634,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E59" s="3">
         <v>25200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>27600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E60" s="3">
         <v>28300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>24600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22200</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3787,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3686,11 +3829,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3709,50 +3852,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E62" s="3">
         <v>35500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>45800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>42100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>44800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>45900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30400</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E66" s="3">
         <v>63800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>59300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>80200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>69200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>72900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>74700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>73500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4203,13 +4371,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>150200</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-340500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-299300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-264800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-254800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-225300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-197200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-170200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-143600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-116900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-97800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-79300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-58300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-44000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>343300</v>
+      </c>
+      <c r="E76" s="3">
         <v>368400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>398300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>269500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>278300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>300900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>324100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>347900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>371800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>387800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>404400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-47700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-35700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3">
         <v>-9800</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4825,25 +5024,25 @@
         <v>700</v>
       </c>
       <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
         <v>1600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
       </c>
       <c r="J83" s="3">
+        <v>500</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
@@ -4852,7 +5051,7 @@
         <v>300</v>
       </c>
       <c r="N83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -4869,8 +5068,8 @@
       <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>200</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-28800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,47 +5494,48 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-700</v>
       </c>
       <c r="L91" s="3">
         <v>-700</v>
       </c>
       <c r="M91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -5322,22 +5543,25 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-68500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>20700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-72100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-174000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>7000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,61 +6037,64 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>135100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>322700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>109700</v>
-      </c>
-      <c r="P100" s="3">
-        <v>100</v>
       </c>
       <c r="Q100" s="3">
         <v>100</v>
       </c>
       <c r="R100" s="3">
+        <v>100</v>
+      </c>
+      <c r="S100" s="3">
         <v>-1500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -5856,8 +6102,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5918,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-52900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>37900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-35500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-92800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-194900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>305800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>130000</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-8600</v>
       </c>
       <c r="Q102" s="3">
         <v>-8600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="R102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-2300</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3">
         <v>1700</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,8 +890,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +958,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,73 +986,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E12" s="3">
         <v>33800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>25700</v>
       </c>
       <c r="I12" s="3">
         <v>25700</v>
       </c>
       <c r="J12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K12" s="3">
         <v>20000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8600</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1120,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1123,8 +1143,8 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1132,21 +1152,21 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-1600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1159,8 +1179,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1168,8 +1188,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1233,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,138 +1281,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E17" s="3">
         <v>48400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>41000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-46000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-37400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-32800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-31100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-10400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,138 +1443,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1700</v>
       </c>
       <c r="L20" s="3">
         <v>1700</v>
       </c>
       <c r="M20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-40500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-33600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-27500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-20700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-10800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1569,8 +1609,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1596,8 +1636,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1605,109 +1645,115 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-41200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-26900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1715,28 +1761,31 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-41200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3">
         <v>-9800</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-41200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3">
         <v>-9800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,138 +2257,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1700</v>
       </c>
       <c r="L32" s="3">
         <v>-1700</v>
       </c>
       <c r="M32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-41200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3">
         <v>-9800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-41200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3">
         <v>-9800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,53 +2656,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E41" s="3">
         <v>49400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>104100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>66200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>58300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>112100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>147600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>240400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>435300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>129500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>145900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,44 +2722,47 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>223800</v>
+      </c>
+      <c r="E42" s="3">
         <v>244600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>277700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>234400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>193000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>175800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>189300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>211300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>227800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>206100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>135400</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2685,8 +2775,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2700,53 +2790,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E43" s="3">
         <v>3600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,8 +2858,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2830,53 +2926,56 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E45" s="3">
         <v>6900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,53 +2994,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>270900</v>
+      </c>
+      <c r="E46" s="3">
         <v>304500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>338800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>350700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>268500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>239500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>260200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>306900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>352900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>368000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>391200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>449000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>143000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>155900</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,43 +3062,46 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E47" s="3">
         <v>59700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>51300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>66000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>41100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>70100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>77100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>57000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>33900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45300</v>
-      </c>
-      <c r="N47" s="3">
-        <v>7600</v>
       </c>
       <c r="O47" s="3">
         <v>7600</v>
@@ -3004,8 +3109,8 @@
       <c r="P47" s="3">
         <v>7600</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>7600</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -3025,53 +3130,56 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E48" s="3">
         <v>40800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,8 +3198,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,53 +3402,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1600</v>
       </c>
       <c r="F52" s="3">
         <v>1600</v>
       </c>
       <c r="G52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H52" s="3">
         <v>1400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1500</v>
       </c>
       <c r="I52" s="3">
         <v>1500</v>
       </c>
       <c r="J52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="K52" s="3">
         <v>1300</v>
       </c>
       <c r="L52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,53 +3538,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>372900</v>
+      </c>
+      <c r="E54" s="3">
         <v>406800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>432200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>457500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>349600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>347500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>373800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>398800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>421400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>446000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>442400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>462000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>158400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>168000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3606,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,53 +3660,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>5900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3726,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3637,11 +3771,11 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,53 +3794,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E59" s="3">
         <v>23100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>27000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,53 +3862,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E60" s="3">
         <v>29000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,8 +3930,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3832,11 +3975,11 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3855,53 +3998,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E62" s="3">
         <v>34500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>44800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>45900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>44600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>47500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,53 +4270,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E66" s="3">
         <v>63500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>80200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>72900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>57600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4338,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4374,13 +4542,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>150200</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -4400,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,53 +4636,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-378200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-340500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-299300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-264800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-254800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-225300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-197200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-170200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-143600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-116900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-97800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-79300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-58300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4704,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,53 +4908,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>310500</v>
+      </c>
+      <c r="E76" s="3">
         <v>343300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>368400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>398300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>269500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>278300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>300900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>324100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>347900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>371800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>387800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>404400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-47700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4976,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-41200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3">
         <v>-9800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,37 +5213,38 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
       </c>
       <c r="F83" s="3">
+        <v>700</v>
+      </c>
+      <c r="G83" s="3">
         <v>1600</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
       </c>
       <c r="I83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
       </c>
       <c r="K83" s="3">
+        <v>500</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
@@ -5054,7 +5253,7 @@
         <v>300</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
@@ -5071,8 +5270,8 @@
       <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>200</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5080,8 +5279,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-37200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>20300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,50 +5715,51 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-700</v>
       </c>
       <c r="M91" s="3">
         <v>-700</v>
       </c>
       <c r="N91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -5546,22 +5767,25 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,73 +5917,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E94" s="3">
         <v>23000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>11100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>20700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-72100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-174000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>7000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5845,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,64 +6283,67 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>12500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>135100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>322700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>109700</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>100</v>
       </c>
       <c r="R100" s="3">
         <v>100</v>
       </c>
       <c r="S100" s="3">
+        <v>100</v>
+      </c>
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6105,8 +6351,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6170,69 +6419,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-52900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>37900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-35500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-92800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-194900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>305800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>130000</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-8600</v>
       </c>
       <c r="R102" s="3">
         <v>-8600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="S102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>-2300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,200 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
         <v>1700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>35500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>33800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>31300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>28600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>26500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>25700</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -893,31 +900,34 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-22200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -961,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E12" s="3">
         <v>35500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>28600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>25700</v>
       </c>
       <c r="J12" s="3">
         <v>25700</v>
       </c>
       <c r="K12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="L12" s="3">
         <v>20000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8600</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,28 +1140,31 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1155,21 +1175,21 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1182,8 +1202,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1191,31 +1211,34 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1259,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E17" s="3">
         <v>47000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-46000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14600</v>
       </c>
-      <c r="H18" s="3">
-        <v>-32800</v>
-      </c>
       <c r="I18" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-31100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-30600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-26500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-20400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-10400</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,144 +1477,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5800</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>4800</v>
+        <v>-1800</v>
       </c>
       <c r="F20" s="3">
-        <v>3100</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="3">
-        <v>4600</v>
+        <v>-13800</v>
       </c>
       <c r="H20" s="3">
-        <v>3300</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>3100</v>
+        <v>-300</v>
       </c>
       <c r="J20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K20" s="3">
         <v>3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1700</v>
       </c>
       <c r="M20" s="3">
         <v>1700</v>
       </c>
       <c r="N20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-36800</v>
+        <v>-32700</v>
       </c>
       <c r="E21" s="3">
-        <v>-40500</v>
+        <v>-40900</v>
       </c>
       <c r="F21" s="3">
-        <v>-33600</v>
+        <v>-45000</v>
       </c>
       <c r="G21" s="3">
-        <v>-8400</v>
+        <v>-22900</v>
       </c>
       <c r="H21" s="3">
-        <v>-28900</v>
+        <v>-13200</v>
       </c>
       <c r="I21" s="3">
-        <v>-27500</v>
+        <v>-32000</v>
       </c>
       <c r="J21" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-26400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-20700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-12900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-10800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1612,8 +1652,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1639,8 +1679,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1648,76 +1688,82 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-37700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-41200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-34300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-29500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1727,36 +1773,36 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1764,28 +1810,31 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1200</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-41200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-19100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3">
         <v>-9800</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-37700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-41200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-27000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3">
         <v>-9800</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5800</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-4800</v>
+        <v>1800</v>
       </c>
       <c r="F32" s="3">
-        <v>-3100</v>
+        <v>300</v>
       </c>
       <c r="G32" s="3">
-        <v>-4600</v>
+        <v>13800</v>
       </c>
       <c r="H32" s="3">
-        <v>-3300</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>-3100</v>
+        <v>300</v>
       </c>
       <c r="J32" s="3">
+        <v>300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1700</v>
       </c>
       <c r="M32" s="3">
         <v>-1700</v>
       </c>
       <c r="N32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-41200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3">
         <v>-9800</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-41200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3">
         <v>-9800</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,56 +2743,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E41" s="3">
         <v>37900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>104100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>66200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>58300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>147600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>240400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>435300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>129500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>145900</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,47 +2812,50 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E42" s="3">
         <v>223800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>244600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>277700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>234400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>193000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>175800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>189300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>211300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>227800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>206100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>135400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,8 +2868,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2793,56 +2883,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2861,31 +2954,34 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2929,56 +3025,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6300</v>
+        <v>2200</v>
       </c>
       <c r="E45" s="3">
-        <v>6900</v>
+        <v>2400</v>
       </c>
       <c r="F45" s="3">
-        <v>6200</v>
+        <v>1800</v>
       </c>
       <c r="G45" s="3">
-        <v>7100</v>
+        <v>1200</v>
       </c>
       <c r="H45" s="3">
-        <v>5600</v>
+        <v>2200</v>
       </c>
       <c r="I45" s="3">
-        <v>6100</v>
+        <v>2100</v>
       </c>
       <c r="J45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K45" s="3">
         <v>7900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,56 +3096,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>237400</v>
+      </c>
+      <c r="E46" s="3">
         <v>270900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>304500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>338800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>350700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>268500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>239500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>260200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>306900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>352900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>368000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>391200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>449000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>143000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>155900</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,46 +3167,49 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>62100</v>
+      </c>
+      <c r="E47" s="3">
         <v>59400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>59700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>51300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>66000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>70100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>77100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>57000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>45300</v>
-      </c>
-      <c r="O47" s="3">
-        <v>7600</v>
       </c>
       <c r="P47" s="3">
         <v>7600</v>
@@ -3112,8 +3217,8 @@
       <c r="Q47" s="3">
         <v>7600</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>7600</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3133,56 +3238,59 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E48" s="3">
         <v>41000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,8 +3309,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3269,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,56 +3522,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1600</v>
       </c>
       <c r="G52" s="3">
         <v>1600</v>
       </c>
       <c r="H52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I52" s="3">
         <v>1400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1500</v>
       </c>
       <c r="J52" s="3">
         <v>1500</v>
       </c>
       <c r="K52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="L52" s="3">
         <v>1300</v>
       </c>
       <c r="M52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N52" s="3">
         <v>1500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,56 +3664,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>344300</v>
+      </c>
+      <c r="E54" s="3">
         <v>372900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>406800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>432200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>457500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>349600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>347500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>373800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>398800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>421400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>446000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>442400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>462000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>158400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>168000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,56 +3791,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3729,31 +3860,34 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3774,11 +3908,11 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,56 +3931,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>27700</v>
+        <v>7700</v>
       </c>
       <c r="E59" s="3">
-        <v>23100</v>
+        <v>4900</v>
       </c>
       <c r="F59" s="3">
-        <v>25200</v>
+        <v>4600</v>
       </c>
       <c r="G59" s="3">
-        <v>22200</v>
+        <v>4300</v>
       </c>
       <c r="H59" s="3">
-        <v>29900</v>
+        <v>4900</v>
       </c>
       <c r="I59" s="3">
-        <v>24400</v>
+        <v>14900</v>
       </c>
       <c r="J59" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K59" s="3">
         <v>27000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,56 +4002,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E60" s="3">
         <v>30900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>24600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,31 +4073,34 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>26300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>26200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3978,11 +4121,11 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4001,56 +4144,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>31500</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
-        <v>34500</v>
+        <v>800</v>
       </c>
       <c r="F62" s="3">
-        <v>35500</v>
+        <v>2600</v>
       </c>
       <c r="G62" s="3">
-        <v>34700</v>
+        <v>2900</v>
       </c>
       <c r="H62" s="3">
-        <v>45800</v>
+        <v>1300</v>
       </c>
       <c r="I62" s="3">
-        <v>42100</v>
+        <v>1100</v>
       </c>
       <c r="J62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K62" s="3">
         <v>44800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>45900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>44600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>31400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>29900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,56 +4428,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E66" s="3">
         <v>62500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>59300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>80200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>69200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>74200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>57600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4545,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>150200</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -4571,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,56 +4810,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-412900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-378200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-340500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-299300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-264800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-254800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-225300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-197200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-170200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-143600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-116900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-97800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-79300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-58300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-44000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,56 +5094,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>281200</v>
+      </c>
+      <c r="E76" s="3">
         <v>310500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>343300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>368400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>398300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>269500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>278300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>300900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>324100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>347900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>371800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>387800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>404400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-47700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-35700</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-41200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3">
         <v>-9800</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,40 +5412,41 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="E83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
       </c>
       <c r="L83" s="3">
+        <v>500</v>
+      </c>
+      <c r="M83" s="3">
         <v>400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
@@ -5256,7 +5455,7 @@
         <v>300</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -5273,8 +5472,8 @@
       <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>200</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5282,8 +5481,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-37200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,53 +5936,54 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-700</v>
       </c>
       <c r="N91" s="3">
         <v>-700</v>
       </c>
       <c r="O91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -5770,22 +5991,25 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E94" s="3">
         <v>21200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>23000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>11100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>20700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-72100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-174000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>7000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,31 +6247,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6082,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,67 +6529,70 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>135100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>322700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>109700</v>
-      </c>
-      <c r="R100" s="3">
-        <v>100</v>
       </c>
       <c r="S100" s="3">
         <v>100</v>
       </c>
       <c r="T100" s="3">
+        <v>100</v>
+      </c>
+      <c r="U100" s="3">
         <v>-1500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6354,31 +6600,34 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6422,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-52900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>37900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-35500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-92800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-194900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>305800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>130000</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-8600</v>
       </c>
       <c r="S102" s="3">
         <v>-8600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="T102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3">
         <v>-2300</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E8" s="3">
         <v>2000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3">
         <v>1700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E9" s="3">
         <v>29800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25700</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,8 +909,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -912,26 +921,26 @@
         <v>-27800</v>
       </c>
       <c r="E10" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F10" s="3">
         <v>-32000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-31400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-27700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-4900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-22700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-22200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -974,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E12" s="3">
         <v>30400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>35500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>28600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>25700</v>
       </c>
       <c r="K12" s="3">
         <v>25700</v>
       </c>
       <c r="L12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="M12" s="3">
         <v>20000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8600</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,22 +1159,25 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>4500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1178,21 +1197,21 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1205,8 +1224,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1214,8 +1233,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1223,25 +1245,25 @@
         <v>1200</v>
       </c>
       <c r="E15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
-      </c>
-      <c r="F15" s="3">
-        <v>700</v>
       </c>
       <c r="G15" s="3">
         <v>700</v>
       </c>
       <c r="H15" s="3">
+        <v>700</v>
+      </c>
+      <c r="I15" s="3">
         <v>1600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1285,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E17" s="3">
         <v>35800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-33700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-46000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-32900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-26500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-20800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-20400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-10400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,150 +1510,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-13800</v>
-      </c>
       <c r="H20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-300</v>
       </c>
       <c r="J20" s="3">
         <v>-300</v>
       </c>
       <c r="K20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L20" s="3">
         <v>3700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1700</v>
       </c>
       <c r="N20" s="3">
         <v>1700</v>
       </c>
       <c r="O20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P20" s="3">
         <v>2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-40900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-45000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-22900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-13200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-30300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-18800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-12900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-10800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1655,8 +1694,8 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1682,8 +1721,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1691,84 +1730,90 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-37700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-41200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-34300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-29500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1776,36 +1821,36 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1813,28 +1858,31 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-37700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-41200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3">
         <v>-9800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-37700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-41200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3">
         <v>-9800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2396,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
-        <v>13800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>300</v>
       </c>
       <c r="J32" s="3">
         <v>300</v>
       </c>
       <c r="K32" s="3">
+        <v>300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1700</v>
       </c>
       <c r="N32" s="3">
         <v>-1700</v>
       </c>
       <c r="O32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-37700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-41200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3">
         <v>-9800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-37700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-41200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3">
         <v>-9800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,59 +2829,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E41" s="3">
         <v>32000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>51200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>104100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>58300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>82100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>147600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>240400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>435300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>129500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>145900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,50 +2901,53 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E42" s="3">
         <v>196200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>223800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>244600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>277700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>234400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>193000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>175800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>189300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>211300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>227800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>206100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>135400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2871,8 +2960,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2886,59 +2975,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3049,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2983,8 +3078,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3028,59 +3123,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,59 +3197,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>219400</v>
+      </c>
+      <c r="E46" s="3">
         <v>237400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>270900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>304500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>338800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>350700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>268500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>239500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>260200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>306900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>352900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>368000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>391200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>449000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>143000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>155900</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,49 +3271,52 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E47" s="3">
         <v>62100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>59400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>51300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>66000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>70100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>77100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>57000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>45300</v>
-      </c>
-      <c r="P47" s="3">
-        <v>7600</v>
       </c>
       <c r="Q47" s="3">
         <v>7600</v>
@@ -3220,8 +3324,8 @@
       <c r="R47" s="3">
         <v>7600</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>7600</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3241,59 +3345,62 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E48" s="3">
         <v>40100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3312,8 +3419,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,59 +3641,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E52" s="3">
         <v>4700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1600</v>
       </c>
       <c r="H52" s="3">
         <v>1600</v>
       </c>
       <c r="I52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J52" s="3">
         <v>1400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1500</v>
       </c>
       <c r="K52" s="3">
         <v>1500</v>
       </c>
       <c r="L52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="M52" s="3">
         <v>1300</v>
       </c>
       <c r="N52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O52" s="3">
         <v>1500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,59 +3789,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>313300</v>
+      </c>
+      <c r="E54" s="3">
         <v>344300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>372900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>406800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>432200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>457500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>349600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>347500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>373800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>398800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>421400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>446000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>442400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>462000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>158400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>168000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,59 +3921,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,35 +3993,38 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1300</v>
       </c>
       <c r="F58" s="3">
         <v>1300</v>
       </c>
       <c r="G58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H58" s="3">
         <v>1200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1100</v>
       </c>
       <c r="I58" s="3">
         <v>1100</v>
       </c>
       <c r="J58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3911,11 +4044,11 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,59 +4067,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E59" s="3">
         <v>7700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,59 +4141,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E60" s="3">
         <v>32200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,35 +4215,38 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25500</v>
+        <v>25100</v>
       </c>
       <c r="E61" s="3">
         <v>25500</v>
       </c>
       <c r="F61" s="3">
-        <v>25900</v>
+        <v>25500</v>
       </c>
       <c r="G61" s="3">
         <v>25900</v>
       </c>
       <c r="H61" s="3">
+        <v>25900</v>
+      </c>
+      <c r="I61" s="3">
         <v>26300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4124,11 +4266,11 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4147,59 +4289,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>44800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>31400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>29900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>30400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,59 +4585,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E66" s="3">
         <v>63100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>62500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>59300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>69200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>54500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>57600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>53500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4716,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>150200</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4742,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,59 +4983,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-448400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-412900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-378200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-340500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-299300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-264800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-254800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-225300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-197200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-170200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-143600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-116900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-97800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-79300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-58300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-44000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,59 +5279,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E76" s="3">
         <v>281200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>310500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>343300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>368400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>398300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>269500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>278300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>300900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>324100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>347900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>371800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>387800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>404400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-47700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-35700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-37700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-41200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3">
         <v>-9800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,43 +5610,44 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>500</v>
       </c>
       <c r="I83" s="3">
+        <v>500</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
       </c>
       <c r="M83" s="3">
+        <v>500</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
@@ -5458,7 +5656,7 @@
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
@@ -5475,8 +5673,8 @@
       <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>200</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5484,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-21400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>20300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9200</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,56 +6156,57 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-700</v>
       </c>
       <c r="O91" s="3">
         <v>-700</v>
       </c>
       <c r="P91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5994,22 +6214,25 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6376,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E94" s="3">
         <v>26500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>21200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>23000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-68500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>11100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>20700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-72100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-174000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>7000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6274,8 +6507,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6319,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,70 +6774,73 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>135100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>322700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>109700</v>
-      </c>
-      <c r="S100" s="3">
-        <v>100</v>
       </c>
       <c r="T100" s="3">
         <v>100</v>
       </c>
       <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -6603,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6629,8 +6877,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6674,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-52900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>37900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-23700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-35500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-92800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-194900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>305800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>130000</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-8600</v>
       </c>
       <c r="T102" s="3">
         <v>-8600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="U102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3">
         <v>-2300</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,220 +656,227 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1200</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3">
         <v>1700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E9" s="3">
         <v>29900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35500</v>
       </c>
-      <c r="G9" s="3">
-        <v>33800</v>
-      </c>
       <c r="H9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I9" s="3">
         <v>31300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25700</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,38 +919,41 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-27800</v>
+        <v>600</v>
       </c>
       <c r="E10" s="3">
         <v>-27800</v>
       </c>
       <c r="F10" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="G10" s="3">
         <v>-32000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-31400</v>
-      </c>
       <c r="H10" s="3">
+        <v>800</v>
+      </c>
+      <c r="I10" s="3">
         <v>-27700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-4900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-22700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-22200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E12" s="3">
         <v>30500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>35500</v>
       </c>
-      <c r="G12" s="3">
-        <v>33800</v>
-      </c>
       <c r="H12" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I12" s="3">
         <v>31300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26500</v>
-      </c>
-      <c r="K12" s="3">
-        <v>25700</v>
       </c>
       <c r="L12" s="3">
         <v>25700</v>
       </c>
       <c r="M12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="N12" s="3">
         <v>20000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8600</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,25 +1179,28 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1200,21 +1220,21 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-1600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1227,8 +1247,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1236,8 +1256,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1248,25 +1271,25 @@
         <v>1200</v>
       </c>
       <c r="F15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G15" s="3">
         <v>900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>700</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
       </c>
       <c r="I15" s="3">
+        <v>700</v>
+      </c>
+      <c r="J15" s="3">
         <v>1600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E17" s="3">
         <v>40400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>29800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12100</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-38300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-43500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-46000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-37400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-32900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-31100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-28400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-20800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-10400</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,8 +1544,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1520,147 +1554,153 @@
         <v>-300</v>
       </c>
       <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-300</v>
       </c>
       <c r="K20" s="3">
         <v>-300</v>
       </c>
       <c r="L20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M20" s="3">
         <v>3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1700</v>
       </c>
       <c r="O20" s="3">
         <v>1700</v>
       </c>
       <c r="P20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q20" s="3">
         <v>2200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-36800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-32700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-40900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-45000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-38200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-32000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-30300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-26300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-18800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-12900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-14800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-10800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1697,8 +1737,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1724,8 +1764,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1733,90 +1773,96 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-37700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-41200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-29500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11000</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1824,36 +1870,36 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1861,28 +1907,31 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-37700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-41200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-29500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3">
         <v>-9800</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-37700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-41200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3">
         <v>-9800</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,8 +2466,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2408,147 +2478,153 @@
         <v>300</v>
       </c>
       <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>300</v>
       </c>
       <c r="K32" s="3">
         <v>300</v>
       </c>
       <c r="L32" s="3">
+        <v>300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1700</v>
       </c>
       <c r="O32" s="3">
         <v>-1700</v>
       </c>
       <c r="P32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-37700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-41200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3">
         <v>-9800</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-37700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-41200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3">
         <v>-9800</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,62 +2916,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E41" s="3">
         <v>16300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>51200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>104100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>58300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>147600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>240400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>435300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>129500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>145900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,53 +2991,56 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E42" s="3">
         <v>193200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>196200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>223800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>244600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>277700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>234400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>193000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>175800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>189300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>211300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>227800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>206100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>135400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2963,8 +3053,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2978,62 +3068,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E43" s="3">
         <v>3300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3081,8 +3177,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3126,62 +3222,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,62 +3299,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>217300</v>
+      </c>
+      <c r="E46" s="3">
         <v>219400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>237400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>270900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>304500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>338800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>350700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>268500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>239500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>260200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>306900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>352900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>368000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>391200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>449000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>143000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>155900</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,52 +3376,55 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E47" s="3">
         <v>49100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>62100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>51300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>66000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>70100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>77100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>57000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>33900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>45300</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>7600</v>
       </c>
       <c r="R47" s="3">
         <v>7600</v>
@@ -3327,8 +3432,8 @@
       <c r="S47" s="3">
         <v>7600</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>7600</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3348,62 +3453,65 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E48" s="3">
         <v>39300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>39300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,8 +3530,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,62 +3761,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1600</v>
       </c>
       <c r="I52" s="3">
         <v>1600</v>
       </c>
       <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1500</v>
       </c>
       <c r="L52" s="3">
         <v>1500</v>
       </c>
       <c r="M52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="N52" s="3">
         <v>1300</v>
       </c>
       <c r="O52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P52" s="3">
         <v>1500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,62 +3915,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E54" s="3">
         <v>313300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>344300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>372900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>406800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>432200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>457500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>349600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>347500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>373800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>398800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>421400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>446000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>442400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>462000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>158400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>168000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,62 +4052,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,38 +4127,41 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1300</v>
       </c>
       <c r="G58" s="3">
         <v>1300</v>
       </c>
       <c r="H58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I58" s="3">
         <v>1200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1100</v>
       </c>
       <c r="J58" s="3">
         <v>1100</v>
       </c>
       <c r="K58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4047,11 +4181,11 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>700</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,62 +4204,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,62 +4281,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E60" s="3">
         <v>30700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,38 +4358,41 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E61" s="3">
         <v>25100</v>
-      </c>
-      <c r="E61" s="3">
-        <v>25500</v>
       </c>
       <c r="F61" s="3">
         <v>25500</v>
       </c>
       <c r="G61" s="3">
-        <v>25900</v>
+        <v>25500</v>
       </c>
       <c r="H61" s="3">
         <v>25900</v>
       </c>
       <c r="I61" s="3">
+        <v>25900</v>
+      </c>
+      <c r="J61" s="3">
         <v>26300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4269,11 +4412,11 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4292,62 +4435,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>44800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>45900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>44600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>47500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>28700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>31400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>29900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>30400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,62 +4743,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E66" s="3">
         <v>60400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>62500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>59300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>80200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>69200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>74700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>54500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>57600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>53500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4886,13 +5054,13 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>150200</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,62 +5157,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-488400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-448400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-412900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-378200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-340500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-299300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-264800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-254800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-225300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-197200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-170200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-143600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-116900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-97800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-79300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-58300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-44000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,62 +5465,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>217200</v>
+      </c>
+      <c r="E76" s="3">
         <v>253000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>281200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>310500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>343300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>368400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>398300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>269500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>278300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>300900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>324100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>347900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>371800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>387800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>404400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-47700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-35700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-37700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-41200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3">
         <v>-9800</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5620,37 +5819,37 @@
         <v>700</v>
       </c>
       <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
         <v>1600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
       </c>
       <c r="J83" s="3">
+        <v>500</v>
+      </c>
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>500</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
       </c>
       <c r="N83" s="3">
+        <v>500</v>
+      </c>
+      <c r="O83" s="3">
         <v>400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>300</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
@@ -5659,7 +5858,7 @@
         <v>300</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
@@ -5676,8 +5875,8 @@
       <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>200</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5685,8 +5884,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-35500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9200</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,59 +6377,60 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-700</v>
       </c>
       <c r="P91" s="3">
         <v>-700</v>
       </c>
       <c r="Q91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R91" s="3">
         <v>-900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -6217,22 +6438,25 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E94" s="3">
         <v>15900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>21200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>23000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-68500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>11100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>20700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-72100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>7000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6510,8 +6744,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,73 +7020,76 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>3900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>135100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>322700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>109700</v>
-      </c>
-      <c r="T100" s="3">
-        <v>100</v>
       </c>
       <c r="U100" s="3">
         <v>100</v>
       </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>-1500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
@@ -6851,8 +7097,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6880,8 +7129,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6925,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-52900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-35500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-92800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-194900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>305800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>130000</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-8600</v>
       </c>
       <c r="U102" s="3">
         <v>-8600</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="V102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3">
         <v>-2300</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,230 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29800</v>
       </c>
-      <c r="G9" s="3">
-        <v>35500</v>
-      </c>
       <c r="H9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25700</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,41 +929,44 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-27800</v>
       </c>
       <c r="F10" s="3">
         <v>-27800</v>
       </c>
       <c r="G10" s="3">
-        <v>-32000</v>
+        <v>-27800</v>
       </c>
       <c r="H10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-27700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-4900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-22700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-22200</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1041,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E12" s="3">
         <v>33800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30400</v>
       </c>
-      <c r="G12" s="3">
-        <v>35500</v>
-      </c>
       <c r="H12" s="3">
+        <v>33500</v>
+      </c>
+      <c r="I12" s="3">
         <v>32200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>31300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>28600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>25700</v>
       </c>
       <c r="M12" s="3">
         <v>25700</v>
       </c>
       <c r="N12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="O12" s="3">
         <v>20000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8600</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,28 +1199,31 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="G14" s="3">
-        <v>100</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1223,21 +1243,21 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-1600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1250,8 +1270,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1259,8 +1279,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1274,25 +1297,25 @@
         <v>1200</v>
       </c>
       <c r="G15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="3">
         <v>900</v>
-      </c>
-      <c r="H15" s="3">
-        <v>700</v>
       </c>
       <c r="I15" s="3">
         <v>700</v>
       </c>
       <c r="J15" s="3">
+        <v>700</v>
+      </c>
+      <c r="K15" s="3">
         <v>1600</v>
-      </c>
-      <c r="K15" s="3">
-        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>600</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1336,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1388,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E17" s="3">
         <v>45300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-42900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-38300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-33700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-43500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-46000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-37400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-30600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-26500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-20400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-15200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,162 +1578,169 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-300</v>
+        <v>8700</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
       </c>
       <c r="F20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-300</v>
       </c>
       <c r="L20" s="3">
         <v>-300</v>
       </c>
       <c r="M20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N20" s="3">
         <v>3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1700</v>
       </c>
       <c r="P20" s="3">
         <v>1700</v>
       </c>
       <c r="Q20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R20" s="3">
         <v>2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-41400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-36800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-32700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-40900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-45000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-32000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-30300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-26200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-20700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-14100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-12900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-14800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1740,8 +1780,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1767,8 +1807,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1776,96 +1816,102 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-34700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-37700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-41200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-34300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1873,36 +1919,36 @@
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1910,28 +1956,31 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-40000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-14700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-40000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-37700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-13200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-14700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7900</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,162 +2536,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>300</v>
+        <v>-8700</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
       </c>
       <c r="F32" s="3">
+        <v>300</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>300</v>
       </c>
       <c r="L32" s="3">
         <v>300</v>
       </c>
       <c r="M32" s="3">
+        <v>300</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1700</v>
       </c>
       <c r="P32" s="3">
         <v>-1700</v>
       </c>
       <c r="Q32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-40000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-13200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-14700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7900</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-40000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-13200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-14700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7900</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,65 +3003,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E41" s="3">
         <v>29400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>51200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>104100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>58300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>112100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>147600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>240400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>435300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>129500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>145900</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,56 +3081,59 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>158700</v>
+      </c>
+      <c r="E42" s="3">
         <v>179000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>193200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>196200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>223800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>244600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>277700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>234400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>193000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>175800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>189300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>211300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>227800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>206100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>135400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3146,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3071,65 +3161,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5800</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3241,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3180,8 +3276,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3225,65 +3321,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E45" s="3">
         <v>2300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,65 +3401,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>192500</v>
+      </c>
+      <c r="E46" s="3">
         <v>217300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>219400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>237400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>270900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>304500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>338800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>350700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>268500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>239500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>260200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>306900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>352900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>368000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>391200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>449000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>143000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>155900</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,55 +3481,58 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
         <v>13300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>49100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>62100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>59700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>51300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>66000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>70100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>77100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>57000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>33900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>45300</v>
-      </c>
-      <c r="R47" s="3">
-        <v>7600</v>
       </c>
       <c r="S47" s="3">
         <v>7600</v>
@@ -3435,8 +3540,8 @@
       <c r="T47" s="3">
         <v>7600</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>7600</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3456,65 +3561,68 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E48" s="3">
         <v>38000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>31800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3641,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,65 +3881,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E52" s="3">
         <v>5000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1600</v>
       </c>
       <c r="J52" s="3">
         <v>1600</v>
       </c>
       <c r="K52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L52" s="3">
         <v>1400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1500</v>
       </c>
       <c r="M52" s="3">
         <v>1500</v>
       </c>
       <c r="N52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="O52" s="3">
         <v>1300</v>
       </c>
       <c r="P52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,65 +4041,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E54" s="3">
         <v>273700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>313300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>344300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>372900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>406800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>432200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>457500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>349600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>347500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>373800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>398800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>421400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>446000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>442400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>462000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>158400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>168000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,65 +4183,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,41 +4261,44 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1300</v>
       </c>
       <c r="H58" s="3">
         <v>1300</v>
       </c>
       <c r="I58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J58" s="3">
         <v>1200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1100</v>
       </c>
       <c r="K58" s="3">
         <v>1100</v>
       </c>
       <c r="L58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4184,11 +4318,11 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,65 +4341,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E59" s="3">
         <v>4400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,65 +4421,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E60" s="3">
         <v>28500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,41 +4501,44 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E61" s="3">
         <v>24300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25100</v>
-      </c>
-      <c r="F61" s="3">
-        <v>25500</v>
       </c>
       <c r="G61" s="3">
         <v>25500</v>
       </c>
       <c r="H61" s="3">
-        <v>25900</v>
+        <v>25500</v>
       </c>
       <c r="I61" s="3">
         <v>25900</v>
       </c>
       <c r="J61" s="3">
+        <v>25900</v>
+      </c>
+      <c r="K61" s="3">
         <v>26300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4415,11 +4558,11 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4438,65 +4581,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>44800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>45900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>28700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>31400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>29900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>30400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4661,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,65 +4901,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E66" s="3">
         <v>56400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>80200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>69200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>53500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5057,13 +5225,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>150200</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -5083,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,65 +5331,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-542500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-488400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-448400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-412900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-378200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-340500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-299300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-264800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-254800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-225300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-197200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-170200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-143600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-116900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-97800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-79300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-58300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-44000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,65 +5651,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>166100</v>
+      </c>
+      <c r="E76" s="3">
         <v>217200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>253000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>281200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>310500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>343300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>368400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>398300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>269500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>278300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>300900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>324100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>347900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>371800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>387800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>404400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-47700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-35700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-40000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-13200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-14700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7900</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,49 +6008,50 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
       </c>
       <c r="F83" s="3">
+        <v>700</v>
+      </c>
+      <c r="G83" s="3">
         <v>1600</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
       </c>
       <c r="I83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
       </c>
       <c r="K83" s="3">
+        <v>500</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>500</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
       </c>
       <c r="O83" s="3">
+        <v>500</v>
+      </c>
+      <c r="P83" s="3">
         <v>400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>300</v>
       </c>
       <c r="Q83" s="3">
         <v>300</v>
@@ -5861,7 +6060,7 @@
         <v>300</v>
       </c>
       <c r="S83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
@@ -5878,8 +6077,8 @@
       <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>200</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -5887,8 +6086,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-36700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-35500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>20300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,62 +6598,63 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-700</v>
       </c>
       <c r="Q91" s="3">
         <v>-700</v>
       </c>
       <c r="R91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="S91" s="3">
         <v>-900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -6441,22 +6662,25 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,85 +6836,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E94" s="3">
         <v>49400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>15900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>26500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>21200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>23000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>11100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>20700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-72100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-174000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>7000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6747,8 +6981,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6792,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,76 +7266,79 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>135100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>322700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>109700</v>
-      </c>
-      <c r="U100" s="3">
-        <v>100</v>
       </c>
       <c r="V100" s="3">
         <v>100</v>
       </c>
       <c r="W100" s="3">
+        <v>100</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
@@ -7100,8 +7346,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7132,8 +7381,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7177,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>13100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-52900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-23700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-30100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-35500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-92800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-194900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>305800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>130000</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-8600</v>
       </c>
       <c r="V102" s="3">
         <v>-8600</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="W102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,250 +656,256 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1200</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="3">
         <v>1700</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1200</v>
+        <v>23800</v>
       </c>
       <c r="E9" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F9" s="3">
         <v>1300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="G9" s="3">
-        <v>29900</v>
-      </c>
       <c r="H9" s="3">
+        <v>30500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>30400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1600</v>
       </c>
-      <c r="I9" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25700</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -942,47 +948,50 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1000</v>
+        <v>-19900</v>
       </c>
       <c r="E10" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="F10" s="3">
         <v>1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="G10" s="3">
-        <v>-27800</v>
-      </c>
       <c r="H10" s="3">
-        <v>400</v>
+        <v>-28400</v>
       </c>
       <c r="I10" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="J10" s="3">
         <v>1500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-27700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-4900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-22700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-22200</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1025,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>21200</v>
+        <v>23800</v>
       </c>
       <c r="E12" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F12" s="3">
         <v>26400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30500</v>
       </c>
-      <c r="H12" s="3">
-        <v>28800</v>
-      </c>
       <c r="I12" s="3">
+        <v>30400</v>
+      </c>
+      <c r="J12" s="3">
         <v>33500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>28600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26500</v>
-      </c>
-      <c r="N12" s="3">
-        <v>25700</v>
       </c>
       <c r="O12" s="3">
         <v>25700</v>
       </c>
       <c r="P12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="Q12" s="3">
         <v>20000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>15800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8600</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,22 +1238,25 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>12200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>500</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1248,8 +1267,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1269,21 +1288,21 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-1600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1296,8 +1315,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1305,16 +1324,19 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>700</v>
+      </c>
+      <c r="E15" s="3">
         <v>600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1200</v>
       </c>
       <c r="F15" s="3">
         <v>1200</v>
@@ -1326,25 +1348,25 @@
         <v>1200</v>
       </c>
       <c r="I15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J15" s="3">
         <v>900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
       </c>
       <c r="L15" s="3">
+        <v>700</v>
+      </c>
+      <c r="M15" s="3">
         <v>1600</v>
-      </c>
-      <c r="M15" s="3">
-        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>600</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1388,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E17" s="3">
         <v>31600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>45300</v>
       </c>
-      <c r="G17" s="3">
-        <v>40400</v>
-      </c>
       <c r="H17" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I17" s="3">
         <v>40300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>48400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>29800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12100</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-35400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-42900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-38300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-38200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-43500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-46000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-32900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-31100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-30600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-20800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-20400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-18600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-14400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,174 +1645,181 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>8700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-300</v>
       </c>
       <c r="G20" s="3">
         <v>-300</v>
       </c>
       <c r="H20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-300</v>
       </c>
       <c r="N20" s="3">
         <v>-300</v>
       </c>
       <c r="O20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P20" s="3">
         <v>3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>1700</v>
       </c>
       <c r="R20" s="3">
         <v>1700</v>
       </c>
       <c r="S20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T20" s="3">
         <v>2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-28800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-43000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-41400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-36800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-37200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-40900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-45000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-38200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-32000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-30300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-18800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-17900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-20700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-14100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-14800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1826,8 +1865,8 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1853,8 +1892,8 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -1862,96 +1901,102 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-54100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-37700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-29500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-21000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-14300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-15100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-600</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1959,11 +2004,11 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1971,36 +2016,36 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2008,28 +2053,31 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-54100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-37700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-41200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-29500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-27000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-19100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-14300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-54100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-40000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-37700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-29500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-21000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-14300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2675,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-8700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>300</v>
       </c>
       <c r="G32" s="3">
         <v>300</v>
       </c>
       <c r="H32" s="3">
+        <v>300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>300</v>
       </c>
       <c r="N32" s="3">
         <v>300</v>
       </c>
       <c r="O32" s="3">
+        <v>300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-1700</v>
       </c>
       <c r="R32" s="3">
         <v>-1700</v>
       </c>
       <c r="S32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="T32" s="3">
         <v>-2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-54100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-37700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-29500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-19100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-21000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-14300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-54100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-37700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-29500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-19100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-21000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-14300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,71 +3176,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E41" s="3">
         <v>11100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>51200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>104100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>58300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>82100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>112100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>147600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>240400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>435300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>129500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>145900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,62 +3260,65 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E42" s="3">
         <v>136100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>158700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>179000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>193200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>196200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>223800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>244600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>277700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>234400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>193000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>175800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>189300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>211300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>227800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>206100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>135400</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3242,8 +3331,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3257,71 +3346,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,8 +3432,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3378,8 +3473,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3423,71 +3518,74 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>3400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,71 +3604,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E46" s="3">
         <v>155500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>192500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>217300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>219400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>237400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>270900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>304500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>338800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>350700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>268500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>239500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>260200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>306900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>352900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>368000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>391200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>449000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>143000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>155900</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,61 +3690,64 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E47" s="3">
         <v>12100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>49100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>62100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>59400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>59700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>51300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>66000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>41100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>70100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>77100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>57000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>33900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>44800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>45300</v>
-      </c>
-      <c r="T47" s="3">
-        <v>7600</v>
       </c>
       <c r="U47" s="3">
         <v>7600</v>
@@ -3651,8 +3755,8 @@
       <c r="V47" s="3">
         <v>7600</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>7600</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3672,71 +3776,74 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E48" s="3">
         <v>23600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>40800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>39300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>33600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>31800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3755,8 +3862,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3838,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,71 +4120,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E52" s="3">
         <v>3800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1600</v>
       </c>
       <c r="L52" s="3">
         <v>1600</v>
       </c>
       <c r="M52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N52" s="3">
         <v>1400</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1500</v>
       </c>
       <c r="O52" s="3">
         <v>1500</v>
       </c>
       <c r="P52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="Q52" s="3">
         <v>1300</v>
       </c>
       <c r="R52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S52" s="3">
         <v>1500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,71 +4292,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>175400</v>
+      </c>
+      <c r="E54" s="3">
         <v>195000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>220900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>273700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>313300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>344300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>372900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>406800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>432200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>457500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>349600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>347500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>373800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>398800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>421400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>446000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>442400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>462000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>158400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>168000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,71 +4444,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4398,47 +4528,50 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1300</v>
       </c>
       <c r="J58" s="3">
         <v>1300</v>
       </c>
       <c r="K58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L58" s="3">
         <v>1200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1100</v>
       </c>
       <c r="M58" s="3">
         <v>1100</v>
       </c>
       <c r="N58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4458,11 +4591,11 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4481,71 +4614,74 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E59" s="3">
         <v>4100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4564,71 +4700,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E60" s="3">
         <v>28100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>22200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,47 +4786,50 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E61" s="3">
         <v>22800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25100</v>
-      </c>
-      <c r="H61" s="3">
-        <v>25500</v>
       </c>
       <c r="I61" s="3">
         <v>25500</v>
       </c>
       <c r="J61" s="3">
-        <v>25900</v>
+        <v>25500</v>
       </c>
       <c r="K61" s="3">
         <v>25900</v>
       </c>
       <c r="L61" s="3">
+        <v>25900</v>
+      </c>
+      <c r="M61" s="3">
         <v>26300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4707,11 +4849,11 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>900</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4730,8 +4872,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4741,60 +4886,60 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>45900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>44600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>28700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>31400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>29900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>30400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4813,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,71 +5216,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E66" s="3">
         <v>53100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>56400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>62500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>69200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>73500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>74200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>54500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>57600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>53500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5399,13 +5566,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>150200</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5425,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,71 +5678,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-596500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-570000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-542500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-488400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-448400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-412900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-378200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-340500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-299300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-264800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-254800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-225300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-197200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-170200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-143600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-116900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-97800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-79300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-58300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-44000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,71 +6022,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E76" s="3">
         <v>141800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>166100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>217200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>253000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>281200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>310500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>343300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>368400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>398300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>269500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>278300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>300900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>324100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>347900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>371800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>387800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>404400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-47700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-35700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-54100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-37700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-29500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-19100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-21000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-14300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6405,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6217,46 +6415,46 @@
         <v>1200</v>
       </c>
       <c r="E83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F83" s="3">
         <v>900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>700</v>
       </c>
       <c r="G83" s="3">
         <v>700</v>
       </c>
       <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
         <v>1600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
       </c>
       <c r="K83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
       </c>
       <c r="M83" s="3">
+        <v>500</v>
+      </c>
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
       </c>
       <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+      <c r="R83" s="3">
         <v>400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
@@ -6265,7 +6463,7 @@
         <v>300</v>
       </c>
       <c r="U83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
@@ -6282,8 +6480,8 @@
       <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>200</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -6291,8 +6489,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6919,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-28300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-36700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-37200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-27900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-21400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,68 +7039,69 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-700</v>
       </c>
       <c r="S91" s="3">
         <v>-700</v>
       </c>
       <c r="T91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U91" s="3">
         <v>-900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -6889,22 +7109,25 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7295,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E94" s="3">
         <v>10900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>49400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>15900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>26500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>21200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>23000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-68500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>20700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-72100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-174000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>7000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7221,8 +7454,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7266,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,82 +7757,85 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>135100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>17600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>322700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>109700</v>
-      </c>
-      <c r="W100" s="3">
-        <v>100</v>
       </c>
       <c r="X100" s="3">
         <v>100</v>
       </c>
       <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
@@ -7598,8 +7843,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7636,8 +7884,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7681,87 +7929,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-52900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>37900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-23700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-35500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-92800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-194900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>305800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>130000</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-8600</v>
       </c>
       <c r="X102" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Y102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>CRBU</t>
   </si>
@@ -656,259 +656,266 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="3">
         <v>1700</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>23800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22400</v>
       </c>
-      <c r="F9" s="3">
-        <v>1300</v>
-      </c>
       <c r="G9" s="3">
-        <v>1700</v>
+        <v>27700</v>
       </c>
       <c r="H9" s="3">
+        <v>35500</v>
+      </c>
+      <c r="I9" s="3">
         <v>30500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -951,50 +958,53 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-19900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-20200</v>
       </c>
-      <c r="F10" s="3">
-        <v>1400</v>
-      </c>
       <c r="G10" s="3">
-        <v>600</v>
+        <v>-25000</v>
       </c>
       <c r="H10" s="3">
-        <v>-28400</v>
+        <v>-33200</v>
       </c>
       <c r="I10" s="3">
         <v>-28400</v>
       </c>
       <c r="J10" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="K10" s="3">
         <v>1500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-27700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-4900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-22700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-22200</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,94 +1082,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E12" s="3">
         <v>23800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22400</v>
       </c>
-      <c r="F12" s="3">
-        <v>26400</v>
-      </c>
       <c r="G12" s="3">
-        <v>33800</v>
+        <v>27700</v>
       </c>
       <c r="H12" s="3">
+        <v>35500</v>
+      </c>
+      <c r="I12" s="3">
         <v>30500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26500</v>
-      </c>
-      <c r="O12" s="3">
-        <v>25700</v>
       </c>
       <c r="P12" s="3">
         <v>25700</v>
       </c>
       <c r="Q12" s="3">
+        <v>25700</v>
+      </c>
+      <c r="R12" s="3">
         <v>20000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>15100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>15800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8600</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,23 +1258,26 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>12200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,8 +1290,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1291,21 +1311,21 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-1600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1338,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1327,19 +1347,22 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1200</v>
       </c>
       <c r="G15" s="3">
         <v>1200</v>
@@ -1351,25 +1374,25 @@
         <v>1200</v>
       </c>
       <c r="J15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K15" s="3">
         <v>900</v>
-      </c>
-      <c r="K15" s="3">
-        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
       </c>
       <c r="M15" s="3">
+        <v>700</v>
+      </c>
+      <c r="N15" s="3">
         <v>1600</v>
-      </c>
-      <c r="N15" s="3">
-        <v>600</v>
       </c>
       <c r="O15" s="3">
         <v>600</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E17" s="3">
         <v>32400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>31600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>48400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>41000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>34300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>29800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12100</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-28500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-35400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-38900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-38200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-43500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-28400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-20800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-20400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-18600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-14400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,180 +1679,187 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>8700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-300</v>
       </c>
       <c r="H20" s="3">
         <v>-300</v>
       </c>
       <c r="I20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-300</v>
       </c>
       <c r="O20" s="3">
         <v>-300</v>
       </c>
       <c r="P20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1700</v>
       </c>
       <c r="S20" s="3">
         <v>1700</v>
       </c>
       <c r="T20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U20" s="3">
         <v>2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="Z20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-27700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-28800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-43000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-41400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-37400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-37200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-40900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-45000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-38200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-32000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-30300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-26300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-20700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-14100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1868,8 +1908,8 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1895,8 +1935,8 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -1904,114 +1944,120 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-54100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-34700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-37700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-41200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-29500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-21000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-14300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-15100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-600</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -2019,36 +2065,36 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2056,28 +2102,31 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-26500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-54100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-37700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-29500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-19100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-14300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-13200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-26500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-54100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-37700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-29500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-14300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-13200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,180 +2745,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>-8700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>300</v>
       </c>
       <c r="H32" s="3">
         <v>300</v>
       </c>
       <c r="I32" s="3">
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>300</v>
       </c>
       <c r="O32" s="3">
         <v>300</v>
       </c>
       <c r="P32" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-1700</v>
       </c>
       <c r="S32" s="3">
         <v>-1700</v>
       </c>
       <c r="T32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="U32" s="3">
         <v>-2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="Z32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-26500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-54100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-37700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-29500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-19100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-14300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-13200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-26500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-54100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-37700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-29500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-19100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-14300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-13200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,74 +3263,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E41" s="3">
         <v>12400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>66200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>58300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>82100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>112100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>147600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>240400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>435300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>129500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>145900</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,65 +3350,68 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>105600</v>
+      </c>
+      <c r="E42" s="3">
         <v>127000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>136100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>158700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>179000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>193200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>196200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>223800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>244600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>277700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>234400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>193000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>175800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>189300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>211300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>227800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>206100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>135400</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3334,8 +3424,8 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3349,74 +3439,77 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E43" s="3">
         <v>3000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5800</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3435,8 +3528,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3476,8 +3572,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3521,74 +3617,77 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>3400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4200</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,74 +3706,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>122400</v>
+      </c>
+      <c r="E46" s="3">
         <v>145200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>192500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>217300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>219400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>237400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>270900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>304500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>338800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>350700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>268500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>239500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>260200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>306900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>352900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>368000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>391200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>449000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>143000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>155900</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,64 +3795,67 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>62100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>59400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>59700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>51300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>66000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>70100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>77100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>57000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>33900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>45300</v>
-      </c>
-      <c r="U47" s="3">
-        <v>7600</v>
       </c>
       <c r="V47" s="3">
         <v>7600</v>
@@ -3758,8 +3863,8 @@
       <c r="W47" s="3">
         <v>7600</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>7600</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
@@ -3779,74 +3884,77 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E48" s="3">
         <v>24400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>39300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>33300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>31800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3400</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3973,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,74 +4240,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1600</v>
       </c>
       <c r="M52" s="3">
         <v>1600</v>
       </c>
       <c r="N52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O52" s="3">
         <v>1400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1500</v>
       </c>
       <c r="P52" s="3">
         <v>1500</v>
       </c>
       <c r="Q52" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="R52" s="3">
         <v>1300</v>
       </c>
       <c r="S52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T52" s="3">
         <v>1500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,74 +4418,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E54" s="3">
         <v>175400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>195000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>220900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>273700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>313300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>344300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>372900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>406800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>432200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>457500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>349600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>347500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>373800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>398800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>421400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>446000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>442400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>462000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>158400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>168000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,74 +4575,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>5800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,50 +4662,53 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1300</v>
       </c>
       <c r="K58" s="3">
         <v>1300</v>
       </c>
       <c r="L58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M58" s="3">
         <v>1200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1100</v>
       </c>
       <c r="N58" s="3">
         <v>1100</v>
       </c>
       <c r="O58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4594,11 +4728,11 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4617,74 +4751,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>28400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>24900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,74 +4840,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E60" s="3">
         <v>25400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>25800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>22200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,50 +4929,53 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E61" s="3">
         <v>26000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>25500</v>
       </c>
       <c r="J61" s="3">
         <v>25500</v>
       </c>
       <c r="K61" s="3">
-        <v>25900</v>
+        <v>25500</v>
       </c>
       <c r="L61" s="3">
         <v>25900</v>
       </c>
       <c r="M61" s="3">
+        <v>25900</v>
+      </c>
+      <c r="N61" s="3">
         <v>26300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4852,11 +4995,11 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4875,8 +5018,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4889,60 +5035,60 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>44600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>28700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>31400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>29900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>30400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,74 +5374,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E66" s="3">
         <v>53200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>54800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>56400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>60400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>62500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>80200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>69200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>72900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>74700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>73500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>74200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>54500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>57600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>53500</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5569,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>150200</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>150200</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,74 +5852,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-621600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-596500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-570000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-542500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-488400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-448400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-412900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-378200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-340500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-299300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-264800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-254800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-225300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-197200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-170200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-143600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-116900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-97800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-79300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-58300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-44000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,74 +6208,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E76" s="3">
         <v>122200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>141800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>166100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>217200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>253000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>281200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>310500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>343300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>368400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>398300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>269500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>278300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>300900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>324100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>347900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>371800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>387800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>404400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-47700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-35700</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-26500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-54100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-37700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-29500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-19100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-14300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-13200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,8 +6604,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6418,46 +6617,46 @@
         <v>1200</v>
       </c>
       <c r="F83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G83" s="3">
         <v>900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
         <v>1600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>600</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
       </c>
       <c r="L83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
       </c>
       <c r="N83" s="3">
+        <v>500</v>
+      </c>
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>500</v>
       </c>
       <c r="Q83" s="3">
         <v>500</v>
       </c>
       <c r="R83" s="3">
+        <v>500</v>
+      </c>
+      <c r="S83" s="3">
         <v>400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
@@ -6466,7 +6665,7 @@
         <v>300</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
@@ -6483,8 +6682,8 @@
       <c r="AA83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+      <c r="AB83" s="3">
+        <v>200</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -6492,8 +6691,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,94 +7136,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-25200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-36700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-32900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-37200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-27900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-21700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-15000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-16500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>20300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,71 +7260,72 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-700</v>
       </c>
       <c r="T91" s="3">
         <v>-700</v>
       </c>
       <c r="U91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -7112,22 +7333,25 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,94 +7525,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E94" s="3">
         <v>18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>10900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>49400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>26500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>21200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>23000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-68500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>20700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-72100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-174000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>7000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7649,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7457,8 +7691,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,85 +8003,88 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E100" s="3">
         <v>4100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>135100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>17600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>322700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>109700</v>
-      </c>
-      <c r="X100" s="3">
-        <v>100</v>
       </c>
       <c r="Y100" s="3">
         <v>100</v>
       </c>
       <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
@@ -7846,8 +8092,11 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7887,8 +8136,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7932,90 +8181,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-52900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>37900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-30100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-35500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-92800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-194900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>305800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>130000</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-8600</v>
       </c>
       <c r="Y102" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="Z102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
